--- a/docs/測試用訂單/測試訂單2_A_早上8點.xlsx
+++ b/docs/測試用訂單/測試訂單2_A_早上8點.xlsx
@@ -2587,18 +2587,18 @@
         <v>阿珠小吃：白蝦 1 件＋2 件</v>
       </c>
       <c r="C7" t="str">
-        <v>揀貨合成一項；分貨給阿珠 3 件</v>
+        <v>合成一行 3 件</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>3. 盒數除不盡</v>
+        <v>3. 包裝數量空白</v>
       </c>
       <c r="B8" t="str">
-        <v>晨光早餐店：白蝦 100 盒（每件 14 盒）</v>
+        <v>晨光早餐店：白蝦 100 盒（每件 14 盒，沒寫件數）</v>
       </c>
       <c r="C8" t="str">
-        <v>算成 8 件（7 件又 2 盒，會多拿？）← 請看揀貨單怎麼寫</v>
+        <v>匯入時問件數（100 盒＝7 件又 2 盒）；10 點的改單檔不會再問</v>
       </c>
     </row>
     <row r="9">
@@ -2609,7 +2609,7 @@
         <v>老街麵線：白蝦「50／60」</v>
       </c>
       <c r="C9" t="str">
-        <v>跟別家的「50/60」應該是同一個品項；如果揀貨單分成兩行，就是要修的問題</v>
+        <v>自動換成「50/60」，跟別家的白蝦合在同一行揀</v>
       </c>
     </row>
     <row r="10">
@@ -2620,7 +2620,7 @@
         <v>Kevin Chen：熟白蝦 +2 件、-1 件</v>
       </c>
       <c r="C10" t="str">
-        <v>負數那行不算；目前會出 2 件（實際應該 1 件？）← 請確認鼎新的習慣</v>
+        <v>扣掉退回的，出 1 件</v>
       </c>
     </row>
     <row r="11">
@@ -2631,7 +2631,7 @@
         <v>竹北好食堂：「原本全日，改黑貓」</v>
       </c>
       <c r="C11" t="str">
-        <v>系統會挑先比對到的「全日」← 實際應該黑貓，這是陷阱</v>
+        <v>用「改」後面那家 → 黑貓（兩家都寫、沒寫「改」就會問人）</v>
       </c>
     </row>
     <row r="12">
@@ -2642,7 +2642,7 @@
         <v>誠品商場美食街：「送到誠品信義店B1」；科技大樓：「送科技大樓B1」</v>
       </c>
       <c r="C12" t="str">
-        <v>「誠」被當成「阿誠」、「科技」被當成「科技物流」← 陷阱</v>
+        <v>不會誤認成阿誠、科技物流 → 匯入時問物流商</v>
       </c>
     </row>
     <row r="13">
@@ -2697,7 +2697,7 @@
         <v>補收運費客戶</v>
       </c>
       <c r="C17" t="str">
-        <v>沒有要揀的貨 → 不會排波次</v>
+        <v>跳過，匯入完成時寫「只有運費等費用、沒有貨的 1 張不用揀」</v>
       </c>
     </row>
     <row r="18">
